--- a/feedback_forms/009_movember_participation_survey--feedback_forms.xlsx
+++ b/feedback_forms/009_movember_participation_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'nonprofit'}</t>
+          <t>nonprofit</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Nonprofit'}</t>
+          <t>Nonprofit</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'company'}</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Company'}</t>
+          <t>Company</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'community_group'}</t>
+          <t>community_group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Community group'}</t>
+          <t>Community group</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'help_others'}</t>
+          <t>help_others</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Help others'}</t>
+          <t>Help others</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'be_part_of_something_bigger'}</t>
+          <t>be_part_of_something_bigger</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Be part of something bigger'}</t>
+          <t>Be part of something bigger</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'get_involved_in_the_movember_community'}</t>
+          <t>get_involved_in_the_movember_community</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Get involved in the Movember community'}</t>
+          <t>Get involved in the Movember community</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'undecided'}</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Undecided'}</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'movember_event_participation'}</t>
+          <t>movember_event_participation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Movember event participation'}</t>
+          <t>Movember event participation</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'movember_social_media_engagement'}</t>
+          <t>movember_social_media_engagement</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Movember social media engagement'}</t>
+          <t>Movember social media engagement</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'movember_newsletter_subscription'}</t>
+          <t>movember_newsletter_subscription</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Movember newsletter subscription'}</t>
+          <t>Movember newsletter subscription</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
